--- a/create_pairs_for_pkb_projects_duplicates/output.xlsx
+++ b/create_pairs_for_pkb_projects_duplicates/output.xlsx
@@ -413,162 +413,7052 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>128402</v>
+        <v>78823</v>
       </c>
       <c r="B1" t="n">
-        <v>303087</v>
+        <v>349162</v>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>何良俊;何良俊</t>
+          <t>何耿繩;何耿繩</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128402</v>
+        <v>78890</v>
       </c>
       <c r="B2" t="n">
-        <v>303087</v>
+        <v>349306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>何良俊;何良俊</t>
+          <t>何藻翔;何藻翔</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123984</v>
+        <v>67676</v>
       </c>
       <c r="B3" t="n">
-        <v>124003</v>
+        <v>349266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>王錫爵;王鼎爵</t>
+          <t>何道生;何道生</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126312</v>
+        <v>24874</v>
       </c>
       <c r="B4" t="n">
-        <v>344162</v>
+        <v>98780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>丁奉;丁奉</t>
+          <t>余嶸;余嶸</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>204294</v>
+        <v>55104</v>
       </c>
       <c r="B5" t="n">
-        <v>217187</v>
+        <v>233626</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>秦可大;秦可大</t>
+          <t>侯峒曾;侯峒曾</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92525</v>
+        <v>350290</v>
       </c>
       <c r="B6" t="n">
-        <v>446935</v>
+        <v>440642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>朱長文;朱長文</t>
+          <t>傅景錞;傅景錞</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>326164</v>
+        <v>131603</v>
       </c>
       <c r="B7" t="n">
-        <v>333658</v>
+        <v>350273</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>王夢祥;王夢祥</t>
+          <t>傅朝佑;傅朝佑</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130769</v>
+        <v>11194</v>
       </c>
       <c r="B8" t="n">
-        <v>370687</v>
+        <v>95537</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>陸應龍;陸應龍</t>
+          <t>傅誠;傅誠</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>65871</v>
+        <v>90204</v>
       </c>
       <c r="B9" t="n">
-        <v>126213</v>
+        <v>350455</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>金人瑞;金人瑞</t>
+          <t>儲在文;儲在文</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124003</v>
+        <v>468125</v>
       </c>
       <c r="B10" t="n">
-        <v>326167</v>
+        <v>498496</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>王鼎爵;王鼎爵</t>
+          <t>元孚;元孚</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>32024</v>
+        <v>33562</v>
       </c>
       <c r="B11" t="n">
-        <v>93470</v>
+        <v>356553</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>張彥遠;張彥遠</t>
+          <t>凌廷堪;凌廷堪</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>63361</v>
+      </c>
+      <c r="B12" t="n">
+        <v>356566</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>凌福彭;凌福彭</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123491</v>
+      </c>
+      <c r="B13" t="n">
+        <v>369610</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>劉侗;劉侗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132667</v>
+      </c>
+      <c r="B14" t="n">
+        <v>369266</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>劉元珍;劉元珍</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>75097</v>
+      </c>
+      <c r="B15" t="n">
+        <v>125659</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>劉孚京;劉孚京</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>75066</v>
+      </c>
+      <c r="B16" t="n">
+        <v>369725</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>劉宅俊;劉宅俊</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>475938</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>劉安世;劉安世</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>497632</v>
+      </c>
+      <c r="B18" t="n">
+        <v>505499</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>劉承業;劉承業</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>78930</v>
+      </c>
+      <c r="B19" t="n">
+        <v>494453</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>余鍔;余鍔</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>74867</v>
+      </c>
+      <c r="B20" t="n">
+        <v>370356</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>劉曙;劉曙</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>74954</v>
+      </c>
+      <c r="B21" t="n">
+        <v>370237</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>劉書年;劉書年</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>57389</v>
+      </c>
+      <c r="B22" t="n">
+        <v>370157</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>劉楗;劉楗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>58128</v>
+      </c>
+      <c r="B23" t="n">
+        <v>369658</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>劉綸;劉綸</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>58032</v>
+      </c>
+      <c r="B24" t="n">
+        <v>370067</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>劉藻;劉藻</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>58032</v>
+      </c>
+      <c r="B25" t="n">
+        <v>443301</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>劉藻;劉藻</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>74749</v>
+      </c>
+      <c r="B26" t="n">
+        <v>125636</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>劉開;劉開</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>35180</v>
+      </c>
+      <c r="B27" t="n">
+        <v>75083</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>劉體仁;劉體仁</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>61773</v>
+      </c>
+      <c r="B28" t="n">
+        <v>504739</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>勞乃宣;勞乃宣</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>72249</v>
+      </c>
+      <c r="B29" t="n">
+        <v>369097</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>區湛森;區湛森</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>58410</v>
+      </c>
+      <c r="B30" t="n">
+        <v>442634</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>卿祖培;卿祖培</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>58410</v>
+      </c>
+      <c r="B31" t="n">
+        <v>442634</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>卿祖培;卿祖培</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>92389</v>
+      </c>
+      <c r="B32" t="n">
+        <v>449349</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>史虛白;史虛白</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>56881</v>
+      </c>
+      <c r="B33" t="n">
+        <v>487014</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>史貽直;史貽直</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>258650</v>
+      </c>
+      <c r="B34" t="n">
+        <v>269996</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>吉慶;吉慶</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>35102</v>
+      </c>
+      <c r="B35" t="n">
+        <v>360150</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>姚鼐;姚鼐</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>78633</v>
+      </c>
+      <c r="B36" t="n">
+        <v>352084</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>吳懋政;吳懋政</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>78535</v>
+      </c>
+      <c r="B37" t="n">
+        <v>125645</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>吳敏樹;吳敏樹</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>78259</v>
+      </c>
+      <c r="B38" t="n">
+        <v>351527</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>吳文煥;吳文煥</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>69659</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78593</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>吳穎芳;吳穎芳</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>55276</v>
+      </c>
+      <c r="B40" t="n">
+        <v>125479</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>吳蘭庭;吳蘭庭</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>78357</v>
+      </c>
+      <c r="B41" t="n">
+        <v>352127</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>吳觀禮;吳觀禮</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>78411</v>
+      </c>
+      <c r="B42" t="n">
+        <v>352135</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>吳郁生;吳郁生</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>78479</v>
+      </c>
+      <c r="B43" t="n">
+        <v>352326</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>吳鍾巒;吳鍾巒</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>78057</v>
+      </c>
+      <c r="B44" t="n">
+        <v>351613</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>吳雲;吳雲</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>78144</v>
+      </c>
+      <c r="B45" t="n">
+        <v>351737</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>吳鼎;吳鼎</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>73854</v>
+      </c>
+      <c r="B46" t="n">
+        <v>368023</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>呂夢飛;呂夢飛</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>68453</v>
+      </c>
+      <c r="B47" t="n">
+        <v>291610</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>呂懷;呂懷</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>73795</v>
+      </c>
+      <c r="B48" t="n">
+        <v>367944</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>呂璜;呂璜</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128326</v>
+      </c>
+      <c r="B49" t="n">
+        <v>367956</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>呂維祺;呂維祺</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>83569</v>
+      </c>
+      <c r="B50" t="n">
+        <v>373237</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>周朝槐;周朝槐</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>83366</v>
+      </c>
+      <c r="B51" t="n">
+        <v>373439</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>周光祖;周光祖</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>66176</v>
+      </c>
+      <c r="B52" t="n">
+        <v>372928</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>周紹龍;周紹龍</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>83594</v>
+      </c>
+      <c r="B53" t="n">
+        <v>438828</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>周錫瓚;周錫瓚</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123573</v>
+      </c>
+      <c r="B54" t="n">
+        <v>387355</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>唐文治;唐文治</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129446</v>
+      </c>
+      <c r="B55" t="n">
+        <v>339787</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>唐泰;唐泰</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>68335</v>
+      </c>
+      <c r="B56" t="n">
+        <v>437976</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>唐龍;唐龍</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>68335</v>
+      </c>
+      <c r="B57" t="n">
+        <v>467440</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>唐龍;唐龍</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>89020</v>
+      </c>
+      <c r="B58" t="n">
+        <v>339162</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>商盤;商盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>83890</v>
+      </c>
+      <c r="B59" t="n">
+        <v>368527</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>單作哲;單作哲</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>76338</v>
+      </c>
+      <c r="B60" t="n">
+        <v>368438</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>嚴繩孫;嚴繩孫</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>57458</v>
+      </c>
+      <c r="B61" t="n">
+        <v>344298</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>夏之蓉;夏之蓉</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>55107</v>
+      </c>
+      <c r="B62" t="n">
+        <v>129500</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>夏允彝;夏允彜</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>55110</v>
+      </c>
+      <c r="B63" t="n">
+        <v>124438</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>夏完淳;夏完淳</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>34658</v>
+      </c>
+      <c r="B64" t="n">
+        <v>344376</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>夏尚樸;夏尚樸</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>85517</v>
+      </c>
+      <c r="B65" t="n">
+        <v>360293</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>姚光發;姚光發</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>85517</v>
+      </c>
+      <c r="B66" t="n">
+        <v>487814</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>姚光發;姚光發</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>27889</v>
+      </c>
+      <c r="B67" t="n">
+        <v>35142</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>姚樞;姚樞</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>85253</v>
+      </c>
+      <c r="B68" t="n">
+        <v>374504</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>姜垓;姜垓</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>33182</v>
+      </c>
+      <c r="B69" t="n">
+        <v>374485</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>姜宸英;姜宸英</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>57223</v>
+      </c>
+      <c r="B70" t="n">
+        <v>499885</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>姜晟;姜晟</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>93963</v>
+      </c>
+      <c r="B71" t="n">
+        <v>189486</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>孟簡;孟簡</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>42572</v>
+      </c>
+      <c r="B72" t="n">
+        <v>439059</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>孟賓于;孟賓于</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>42572</v>
+      </c>
+      <c r="B73" t="n">
+        <v>446348</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>孟賓于;孟賓于</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128761</v>
+      </c>
+      <c r="B74" t="n">
+        <v>495524</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>季本;季本</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>83914</v>
+      </c>
+      <c r="B75" t="n">
+        <v>354427</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>宗元醇;宗元醇</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>58670</v>
+      </c>
+      <c r="B76" t="n">
+        <v>123548</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>尹壯圖;尹壯圖</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>72640</v>
+      </c>
+      <c r="B77" t="n">
+        <v>348330</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>尹慶舉;尹慶舉</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126929</v>
+      </c>
+      <c r="B78" t="n">
+        <v>348403</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>尹鳳岐;尹鳳岐</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4142</v>
+      </c>
+      <c r="B79" t="n">
+        <v>450742</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>岳甫;岳甫</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>88852</v>
+      </c>
+      <c r="B80" t="n">
+        <v>350021</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>崔蔚林;崔蔚林</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127031</v>
+      </c>
+      <c r="B81" t="n">
+        <v>357234</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>左光斗;左光斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127031</v>
+      </c>
+      <c r="B82" t="n">
+        <v>498828</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>左光斗;左光斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>32644</v>
+      </c>
+      <c r="B83" t="n">
+        <v>446833</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>崔鄲;崔鄲</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>34649</v>
+      </c>
+      <c r="B84" t="n">
+        <v>224218</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>崔銑;崔銑</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>92292</v>
+      </c>
+      <c r="B85" t="n">
+        <v>447649</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>左偃;左偃</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>88777</v>
+      </c>
+      <c r="B86" t="n">
+        <v>375931</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>常紀;常紀</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>34645</v>
+      </c>
+      <c r="B87" t="n">
+        <v>486524</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>康海;康海</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>54525</v>
+      </c>
+      <c r="B88" t="n">
+        <v>338826</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>廖廷相;廖廷相</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>35048</v>
+      </c>
+      <c r="B89" t="n">
+        <v>345844</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>張之洞;張之洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>130319</v>
+      </c>
+      <c r="B90" t="n">
+        <v>346152</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>張大輪;張大輪</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>80086</v>
+      </c>
+      <c r="B91" t="n">
+        <v>345885</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>張寅;張寅</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>80448</v>
+      </c>
+      <c r="B92" t="n">
+        <v>125622</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>張廷濟;張廷濟</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>34226</v>
+      </c>
+      <c r="B93" t="n">
+        <v>346572</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>張惠言;張惠言</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>80926</v>
+      </c>
+      <c r="B94" t="n">
+        <v>345054</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>張敦仁;張敦仁</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>67223</v>
+      </c>
+      <c r="B95" t="n">
+        <v>130460</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>張益;張益</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>130484</v>
+      </c>
+      <c r="B96" t="n">
+        <v>345660</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>張納陛;張納陛</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>80163</v>
+      </c>
+      <c r="B97" t="n">
+        <v>345407</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>張翯;張翯</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>130419</v>
+      </c>
+      <c r="B98" t="n">
+        <v>345518</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>張肯堂;張肯堂</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>80602</v>
+      </c>
+      <c r="B99" t="n">
+        <v>346393</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>張若采;張若采</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>80602</v>
+      </c>
+      <c r="B100" t="n">
+        <v>441608</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>張若采;張若采</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>79974</v>
+      </c>
+      <c r="B101" t="n">
+        <v>346389</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>張英;張英</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>54432</v>
+      </c>
+      <c r="B102" t="n">
+        <v>345847</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>張之萬;張之萬</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>124309</v>
+      </c>
+      <c r="B103" t="n">
+        <v>305824</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>張位;張位</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>8012</v>
+      </c>
+      <c r="B104" t="n">
+        <v>446009</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>張洎;張洎</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>34791</v>
+      </c>
+      <c r="B105" t="n">
+        <v>131270</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>釋袾宏;釋袾宏</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>68455</v>
+      </c>
+      <c r="B106" t="n">
+        <v>133394</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>顔鯨;顔鯨</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>80172</v>
+      </c>
+      <c r="B107" t="n">
+        <v>345877</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>張謇;張謇</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>80844</v>
+      </c>
+      <c r="B108" t="n">
+        <v>441223</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>張躍鱗;張躍鱗</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>54302</v>
+      </c>
+      <c r="B109" t="n">
+        <v>346957</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>張金鏞;張金鏞</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>80069</v>
+      </c>
+      <c r="B110" t="n">
+        <v>347084</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>張銓;張銓</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>80587</v>
+      </c>
+      <c r="B111" t="n">
+        <v>125638</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>張際亮;張際亮</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>54146</v>
+      </c>
+      <c r="B112" t="n">
+        <v>354107</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>徐人龍;徐人龍</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>16504</v>
+      </c>
+      <c r="B113" t="n">
+        <v>386308</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>徐僑;徐僑</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>86950</v>
+      </c>
+      <c r="B114" t="n">
+        <v>129905</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>徐孚遠;徐孚遠</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>30603</v>
+      </c>
+      <c r="B115" t="n">
+        <v>354004</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>徐松;徐松</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129922</v>
+      </c>
+      <c r="B116" t="n">
+        <v>353830</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>徐汧;徐汧</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>56385</v>
+      </c>
+      <c r="B117" t="n">
+        <v>338406</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>徐熊飛;徐熊飛</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>56385</v>
+      </c>
+      <c r="B118" t="n">
+        <v>441224</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>徐熊飛;徐熊飛</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>86711</v>
+      </c>
+      <c r="B119" t="n">
+        <v>353993</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>徐相;徐相</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>87088</v>
+      </c>
+      <c r="B120" t="n">
+        <v>353955</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>徐葆光;徐葆光</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>30590</v>
+      </c>
+      <c r="B121" t="n">
+        <v>354131</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>徐釚;徐釚</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>86395</v>
+      </c>
+      <c r="B122" t="n">
+        <v>367703</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>恩桂;恩桂</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>35186</v>
+      </c>
+      <c r="B123" t="n">
+        <v>341188</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>施閏章;施閏章</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>35186</v>
+      </c>
+      <c r="B124" t="n">
+        <v>341189</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>施閏章;施閏章</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>30144</v>
+      </c>
+      <c r="B125" t="n">
+        <v>66032</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>朱彜尊;朱彝尊</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>66032</v>
+      </c>
+      <c r="B126" t="n">
+        <v>350788</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>朱彜尊;朱彝尊</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>74286</v>
+      </c>
+      <c r="B127" t="n">
+        <v>350954</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>朱彭壽;朱彭壽</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>29951</v>
+      </c>
+      <c r="B128" t="n">
+        <v>70450</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>朱筠;朱筠</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>35105</v>
+      </c>
+      <c r="B129" t="n">
+        <v>358227</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>李兆洛;李兆洛</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>33848</v>
+      </c>
+      <c r="B130" t="n">
+        <v>374265</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>翁方綱;翁方綱</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>33848</v>
+      </c>
+      <c r="B131" t="n">
+        <v>374265</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>翁方綱;翁方綱</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>35003</v>
+      </c>
+      <c r="B132" t="n">
+        <v>360684</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>董其昌;董其昌</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>91018</v>
+      </c>
+      <c r="B133" t="n">
+        <v>363410</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>蔡念慈;蔡念慈</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>86477</v>
+      </c>
+      <c r="B134" t="n">
+        <v>375108</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>錢以同;錢以同</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>29766</v>
+      </c>
+      <c r="B135" t="n">
+        <v>375110</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>錢儀吉;錢儀吉</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>68547</v>
+      </c>
+      <c r="B136" t="n">
+        <v>308811</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>徐階;徐階</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>91728</v>
+      </c>
+      <c r="B137" t="n">
+        <v>125640</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>戴鈞衡;戴鈞衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>85175</v>
+      </c>
+      <c r="B138" t="n">
+        <v>125620</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>施國祁;施國祁</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>127733</v>
+      </c>
+      <c r="B139" t="n">
+        <v>206085</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>李三才;李三才</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>77456</v>
+      </c>
+      <c r="B140" t="n">
+        <v>359046</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>李因篤;李因篤</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>77882</v>
+      </c>
+      <c r="B141" t="n">
+        <v>358809</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>李翹芬;李翹芬</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>77136</v>
+      </c>
+      <c r="B142" t="n">
+        <v>438192</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>李銳;李銳</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>30301</v>
+      </c>
+      <c r="B143" t="n">
+        <v>359828</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>杭世駿;杭世駿</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>88490</v>
+      </c>
+      <c r="B144" t="n">
+        <v>125634</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>梅曾亮;梅曾亮</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>35124</v>
+      </c>
+      <c r="B145" t="n">
+        <v>125619</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>楊鳳苞;楊鳳苞</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>55684</v>
+      </c>
+      <c r="B146" t="n">
+        <v>353008</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>殷兆鏞;殷兆鏞</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>91372</v>
+      </c>
+      <c r="B147" t="n">
+        <v>352716</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>黎湛枝;黎湛枝</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>91350</v>
+      </c>
+      <c r="B148" t="n">
+        <v>352700</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>黎元寬;黎元寬</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>54133</v>
+      </c>
+      <c r="B149" t="n">
+        <v>118895</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>黃汝亨;黃汝亨</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>54133</v>
+      </c>
+      <c r="B150" t="n">
+        <v>131374</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>黃汝亨;黃汝亨</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>54133</v>
+      </c>
+      <c r="B151" t="n">
+        <v>362772</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>黃汝亨;黃汝亨</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>88250</v>
+      </c>
+      <c r="B152" t="n">
+        <v>362559</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>黃承吉;黃承吉</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>58563</v>
+      </c>
+      <c r="B153" t="n">
+        <v>362891</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>黃彭年;黃彭年</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>88186</v>
+      </c>
+      <c r="B154" t="n">
+        <v>362735</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>黃安濤;黃安濤</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>130219</v>
+      </c>
+      <c r="B155" t="n">
+        <v>338776</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>鹿善繼;鹿善繼</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>90260</v>
+      </c>
+      <c r="B156" t="n">
+        <v>125641</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>魯一同;魯一同</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>35079</v>
+      </c>
+      <c r="B157" t="n">
+        <v>351350</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>魏象樞;魏象樞</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>73590</v>
+      </c>
+      <c r="B158" t="n">
+        <v>355229</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>馮崧生;馮崧生</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>34836</v>
+      </c>
+      <c r="B159" t="n">
+        <v>356833</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>湯斌;湯斌</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>75527</v>
+      </c>
+      <c r="B160" t="n">
+        <v>125637</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>湯鵬;湯鵬</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>90436</v>
+      </c>
+      <c r="B161" t="n">
+        <v>356818</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>溫肅;溫肅</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>54483</v>
+      </c>
+      <c r="B162" t="n">
+        <v>355788</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>潘世恩;潘世恩</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>33903</v>
+      </c>
+      <c r="B163" t="n">
+        <v>355808</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>潘耒;潘耒</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>79511</v>
+      </c>
+      <c r="B164" t="n">
+        <v>125623</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>沈濤;沈濤</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>59090</v>
+      </c>
+      <c r="B165" t="n">
+        <v>356201</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>沈廷芳;沈廷芳</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>79491</v>
+      </c>
+      <c r="B166" t="n">
+        <v>125609</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>沈垚;沈垚</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>66037</v>
+      </c>
+      <c r="B167" t="n">
+        <v>354800</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>江聲;江聲</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>33879</v>
+      </c>
+      <c r="B168" t="n">
+        <v>348836</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>毛奇齡;毛奇齡</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>34013</v>
+      </c>
+      <c r="B169" t="n">
+        <v>367887</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>畢沅;畢沅</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>33176</v>
+      </c>
+      <c r="B170" t="n">
+        <v>357018</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>祁寯藻;祁寯藻</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>85403</v>
+      </c>
+      <c r="B171" t="n">
+        <v>356917</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>祝廷華;祝廷華</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>65833</v>
+      </c>
+      <c r="B172" t="n">
+        <v>352453</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>程晉芳;程晉芳</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>124891</v>
+      </c>
+      <c r="B173" t="n">
+        <v>337944</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>耿定向;耿定向</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>65093</v>
+      </c>
+      <c r="B174" t="n">
+        <v>500186</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>范梁;范梁</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>86241</v>
+      </c>
+      <c r="B175" t="n">
+        <v>125617</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>顧廣譽;顧廣譽</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>126328</v>
+      </c>
+      <c r="B176" t="n">
+        <v>281935</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>丁璣;丁璣</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>74351</v>
+      </c>
+      <c r="B177" t="n">
+        <v>348660</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>喬萊;喬萊</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>67950</v>
+      </c>
+      <c r="B178" t="n">
+        <v>325185</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>張洪;張洪</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>345291</v>
+      </c>
+      <c r="B179" t="n">
+        <v>345292</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>張烈;張烈</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>80069</v>
+      </c>
+      <c r="B180" t="n">
+        <v>347084</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>張銓;張銓</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>310929</v>
+      </c>
+      <c r="B181" t="n">
+        <v>323363</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>張鼎;張鼎</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>88642</v>
+      </c>
+      <c r="B182" t="n">
+        <v>367201</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>戚人鏡;戚人鏡</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>91671</v>
+      </c>
+      <c r="B183" t="n">
+        <v>438302</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>戴易;戴易</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>79932</v>
+      </c>
+      <c r="B184" t="n">
+        <v>438090</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>改琦;改琦</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>72493</v>
+      </c>
+      <c r="B185" t="n">
+        <v>339053</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>方大淳;方大淳</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>72471</v>
+      </c>
+      <c r="B186" t="n">
+        <v>441239</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>方球;方球</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>54685</v>
+      </c>
+      <c r="B187" t="n">
+        <v>374732</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>曾燠;曾燠</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>34349</v>
+      </c>
+      <c r="B188" t="n">
+        <v>438198</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>曾紀鴻;曾紀鴻</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>90350</v>
+      </c>
+      <c r="B189" t="n">
+        <v>374607</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>曾習經;曾習經</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>127408</v>
+      </c>
+      <c r="B190" t="n">
+        <v>307256</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>朱應登;朱應登</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>74275</v>
+      </c>
+      <c r="B191" t="n">
+        <v>125656</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>朱銘盤;朱銘盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>74342</v>
+      </c>
+      <c r="B192" t="n">
+        <v>350608</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>朱麟祺;朱麟祺</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>77358</v>
+      </c>
+      <c r="B193" t="n">
+        <v>357674</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>李孔昭;李孔昭</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>77666</v>
+      </c>
+      <c r="B194" t="n">
+        <v>358187</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>李宗沆;李宗沆</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>77313</v>
+      </c>
+      <c r="B195" t="n">
+        <v>358090</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>李從龍;李從龍</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>77086</v>
+      </c>
+      <c r="B196" t="n">
+        <v>358328</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>李昶;李昶</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>77317</v>
+      </c>
+      <c r="B197" t="n">
+        <v>359199</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>李鳳書;李鳳書</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>77887</v>
+      </c>
+      <c r="B198" t="n">
+        <v>357865</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>李鼎元;李鼎元</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>82649</v>
+      </c>
+      <c r="B199" t="n">
+        <v>364160</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>林春溥;林春溥</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>85992</v>
+      </c>
+      <c r="B200" t="n">
+        <v>363823</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>桂文燿;桂文燿</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>89100</v>
+      </c>
+      <c r="B201" t="n">
+        <v>356004</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>梁士詒;梁士詒</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>76840</v>
+      </c>
+      <c r="B202" t="n">
+        <v>365152</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>楊思聖;楊思聖</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>84946</v>
+      </c>
+      <c r="B203" t="n">
+        <v>439133</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>段光清;段光清</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>75449</v>
+      </c>
+      <c r="B204" t="n">
+        <v>354727</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>江衡;江衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>75496</v>
+      </c>
+      <c r="B205" t="n">
+        <v>354775</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>江逢辰;江逢辰</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>79389</v>
+      </c>
+      <c r="B206" t="n">
+        <v>354894</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>汪孟鋗;汪孟鋗</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>79424</v>
+      </c>
+      <c r="B207" t="n">
+        <v>354842</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>汪康年;汪康年</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>54184</v>
+      </c>
+      <c r="B208" t="n">
+        <v>354887</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>汪廷珍;汪廷珍</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>79454</v>
+      </c>
+      <c r="B209" t="n">
+        <v>354917</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>汪德容;汪德容</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>79232</v>
+      </c>
+      <c r="B210" t="n">
+        <v>355146</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>汪煜;汪煜</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>35043</v>
+      </c>
+      <c r="B211" t="n">
+        <v>355147</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>汪輝祖;汪輝祖</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>54210</v>
+      </c>
+      <c r="B212" t="n">
+        <v>356386</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>沈葆楨;沈葆楨</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>85349</v>
+      </c>
+      <c r="B213" t="n">
+        <v>125602</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>洪頤煊;洪頤煊</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>90463</v>
+      </c>
+      <c r="B214" t="n">
+        <v>357105</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>游光繹;游光繹</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>90466</v>
+      </c>
+      <c r="B215" t="n">
+        <v>357089</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>游紹安;游紹安</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>75519</v>
+      </c>
+      <c r="B216" t="n">
+        <v>125629</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>湯球;湯球</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>90431</v>
+      </c>
+      <c r="B217" t="n">
+        <v>356799</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>溫儀;溫儀</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>132275</v>
+      </c>
+      <c r="B218" t="n">
+        <v>208653</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>熊過;熊過</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>132275</v>
+      </c>
+      <c r="B219" t="n">
+        <v>318293</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>熊過;熊過</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>55786</v>
+      </c>
+      <c r="B220" t="n">
+        <v>342163</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>王仁堪;王仁堪</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>71597</v>
+      </c>
+      <c r="B221" t="n">
+        <v>342667</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>王兆符;王兆符</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>65759</v>
+      </c>
+      <c r="B222" t="n">
+        <v>343570</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>王原祁;王原祁</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>35063</v>
+      </c>
+      <c r="B223" t="n">
+        <v>56833</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>王士禎;王士禛</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>71635</v>
+      </c>
+      <c r="B224" t="n">
+        <v>342592</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>王安瀾;王安瀾</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>35049</v>
+      </c>
+      <c r="B225" t="n">
+        <v>343271</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>王懿榮;王懿榮</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>65762</v>
+      </c>
+      <c r="B226" t="n">
+        <v>343405</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>王掞;王掞</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>72046</v>
+      </c>
+      <c r="B227" t="n">
+        <v>343321</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>王敬銘;王敬銘</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>54580</v>
+      </c>
+      <c r="B228" t="n">
+        <v>341614</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>王文治;王文治</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>33556</v>
+      </c>
+      <c r="B229" t="n">
+        <v>342774</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>王昶;王昶</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>57185</v>
+      </c>
+      <c r="B230" t="n">
+        <v>343223</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>王植;王植</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>71157</v>
+      </c>
+      <c r="B231" t="n">
+        <v>341900</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>王烈;王烈</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>126814</v>
+      </c>
+      <c r="B232" t="n">
+        <v>232115</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>王畿;王畿</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>71200</v>
+      </c>
+      <c r="B233" t="n">
+        <v>341636</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>王章;王章</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>199150</v>
+      </c>
+      <c r="B234" t="n">
+        <v>267619</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>王賓;王賓</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>123984</v>
+      </c>
+      <c r="B235" t="n">
+        <v>333661</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>王錫爵;王錫爵</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>72126</v>
+      </c>
+      <c r="B236" t="n">
+        <v>343817</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>王錫蕃;王錫蕃</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>55233</v>
+      </c>
+      <c r="B237" t="n">
+        <v>367732</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>田雯;田雯</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>73018</v>
+      </c>
+      <c r="B238" t="n">
+        <v>348952</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>盧維慶;盧維慶</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>54731</v>
+      </c>
+      <c r="B239" t="n">
+        <v>344578</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>石韞玉;石韞玉</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>85749</v>
+      </c>
+      <c r="B240" t="n">
+        <v>367061</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>秦恩復;秦恩復</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>85749</v>
+      </c>
+      <c r="B241" t="n">
+        <v>367061</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>秦恩復;秦恩復</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>90288</v>
+      </c>
+      <c r="B242" t="n">
+        <v>338747</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>童棫;童棫</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>91080</v>
+      </c>
+      <c r="B243" t="n">
+        <v>125635</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>管同;管同</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>84561</v>
+      </c>
+      <c r="B244" t="n">
+        <v>365802</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>胡世琦;胡世琦</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>84491</v>
+      </c>
+      <c r="B245" t="n">
+        <v>365894</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>胡煦;胡煦</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>82499</v>
+      </c>
+      <c r="B246" t="n">
+        <v>360777</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>范鄗鼎;范鄗鼎</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>66251</v>
+      </c>
+      <c r="B247" t="n">
+        <v>109721</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>葉琛;葉琛</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>89448</v>
+      </c>
+      <c r="B248" t="n">
+        <v>360552</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>董文驥;董文驥</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>54088</v>
+      </c>
+      <c r="B249" t="n">
+        <v>363296</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>蔡之定;蔡之定</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>90982</v>
+      </c>
+      <c r="B250" t="n">
+        <v>363274</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>蔡升元;蔡升元</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>89685</v>
+      </c>
+      <c r="B251" t="n">
+        <v>361391</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>蔣恭棐;蔣恭棐</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>89543</v>
+      </c>
+      <c r="B252" t="n">
+        <v>361423</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>蔣杲;蔣杲</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>57226</v>
+      </c>
+      <c r="B253" t="n">
+        <v>361343</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>蔣溥;蔣溥</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>76417</v>
+      </c>
+      <c r="B254" t="n">
+        <v>125639</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>蘇惇元;蘇惇元</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>85796</v>
+      </c>
+      <c r="B255" t="n">
+        <v>359645</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>袁佑;袁佑</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>125652</v>
+      </c>
+      <c r="B256" t="n">
+        <v>359672</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>袁寶璜;袁寶璜</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>85881</v>
+      </c>
+      <c r="B257" t="n">
+        <v>359640</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>袁繼梓;袁繼梓</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>63578</v>
+      </c>
+      <c r="B258" t="n">
+        <v>359774</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>袁銑;袁銑</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>91076</v>
+      </c>
+      <c r="B259" t="n">
+        <v>347231</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>裴蔭森;裴蔭森</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>75731</v>
+      </c>
+      <c r="B260" t="n">
+        <v>341308</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>許作屏;許作屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>75782</v>
+      </c>
+      <c r="B261" t="n">
+        <v>341413</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>許振礽;許振礽</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>90620</v>
+      </c>
+      <c r="B262" t="n">
+        <v>340572</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>謝道承;謝道承</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>56569</v>
+      </c>
+      <c r="B263" t="n">
+        <v>366208</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>趙翼;趙翼</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>132207</v>
+      </c>
+      <c r="B264" t="n">
+        <v>289093</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>趙逯;趙逯</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>82269</v>
+      </c>
+      <c r="B265" t="n">
+        <v>348471</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>邵瑛;邵瑛</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>30309</v>
+      </c>
+      <c r="B266" t="n">
+        <v>365423</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>郝懿行;郝懿行</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>87570</v>
+      </c>
+      <c r="B267" t="n">
+        <v>340951</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>郭肇鐄;郭肇鐄</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>79095</v>
+      </c>
+      <c r="B268" t="n">
+        <v>353276</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>鄒嘉來;鄒嘉來</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>79088</v>
+      </c>
+      <c r="B269" t="n">
+        <v>353285</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>鄒植行;鄒植行</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>29589</v>
+      </c>
+      <c r="B270" t="n">
+        <v>329275</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>鄭曉;鄭曉</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>83018</v>
+      </c>
+      <c r="B271" t="n">
+        <v>374138</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>金溶;金溶</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>86410</v>
+      </c>
+      <c r="B272" t="n">
+        <v>375188</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>錢枚;錢枚</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>86491</v>
+      </c>
+      <c r="B273" t="n">
+        <v>375060</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>錢爾登;錢爾登</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>75416</v>
+      </c>
+      <c r="B274" t="n">
+        <v>373826</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>關冕鈞;關冕鈞</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>75418</v>
+      </c>
+      <c r="B275" t="n">
+        <v>373799</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>關賡麟;關賡麟</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>81585</v>
+      </c>
+      <c r="B276" t="n">
+        <v>372373</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>陳介祺;陳介祺</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>81866</v>
+      </c>
+      <c r="B277" t="n">
+        <v>438807</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>陳其元;陳其元</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>54950</v>
+      </c>
+      <c r="B278" t="n">
+        <v>371592</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>陳寶琛;陳寶琛</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>246088</v>
+      </c>
+      <c r="B279" t="n">
+        <v>261926</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>陳璲;陳璲</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>81966</v>
+      </c>
+      <c r="B280" t="n">
+        <v>371491</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>陳紹棠;陳紹棠</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>87852</v>
+      </c>
+      <c r="B281" t="n">
+        <v>373517</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>陶士偰;陶士偰</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>130723</v>
+      </c>
+      <c r="B282" t="n">
+        <v>319011</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>陶承學;陶承學</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>130723</v>
+      </c>
+      <c r="B283" t="n">
+        <v>323316</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>陶承學;陶承學</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>87896</v>
+      </c>
+      <c r="B284" t="n">
+        <v>373530</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>陶春元;陶春元</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>87881</v>
+      </c>
+      <c r="B285" t="n">
+        <v>438265</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>陶汝鼐;陶汝鼐</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>81160</v>
+      </c>
+      <c r="B286" t="n">
+        <v>370744</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>陸以湉;陸以湉</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>81114</v>
+      </c>
+      <c r="B287" t="n">
+        <v>370755</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>陸寅;陸寅</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>81093</v>
+      </c>
+      <c r="B288" t="n">
+        <v>370758</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>陸沅;陸沅</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>33794</v>
+      </c>
+      <c r="B289" t="n">
+        <v>302486</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>陸炳;陸炳</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>33794</v>
+      </c>
+      <c r="B290" t="n">
+        <v>305697</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>陸炳;陸炳</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>132287</v>
+      </c>
+      <c r="B291" t="n">
+        <v>225413</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>雒遵;雒遵</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>89817</v>
+      </c>
+      <c r="B292" t="n">
+        <v>361917</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>韓弼元;韓弼元</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>86359</v>
+      </c>
+      <c r="B293" t="n">
+        <v>355573</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>顧嗣立;顧嗣立</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>86263</v>
+      </c>
+      <c r="B294" t="n">
+        <v>355431</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>顧文彬;顧文彬</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>70992</v>
+      </c>
+      <c r="B295" t="n">
+        <v>369034</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>馬學易;馬學易</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>70908</v>
+      </c>
+      <c r="B296" t="n">
+        <v>368762</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>馬疏;馬疏</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>73525</v>
+      </c>
+      <c r="B297" t="n">
+        <v>355194</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>馮雲驌;馮雲驌</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>73529</v>
+      </c>
+      <c r="B298" t="n">
+        <v>355193</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>馮雲驤;馮雲驤</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>87243</v>
+      </c>
+      <c r="B299" t="n">
+        <v>339230</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>高玢;高玢</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>87245</v>
+      </c>
+      <c r="B300" t="n">
+        <v>339182</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>高詠;高詠</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>91843</v>
+      </c>
+      <c r="B301" t="n">
+        <v>351360</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>魏家驊;魏家驊</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>91833</v>
+      </c>
+      <c r="B302" t="n">
+        <v>351410</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>魏茂林;魏茂林</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>34350</v>
+      </c>
+      <c r="B303" t="n">
+        <v>351284</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>魏裔介;魏裔介</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>90249</v>
+      </c>
+      <c r="B304" t="n">
+        <v>353342</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>魯鴻;魯鴻</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>76244</v>
+      </c>
+      <c r="B305" t="n">
+        <v>357286</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>麥鴻鈞;麥鴻鈞</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>88122</v>
+      </c>
+      <c r="B306" t="n">
+        <v>362986</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>黃本訥;黃本訥</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>68414</v>
+      </c>
+      <c r="B307" t="n">
+        <v>328182</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>黃正色;黃正色</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>72960</v>
+      </c>
+      <c r="B308" t="n">
+        <v>340101</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>龍建章;龍建章</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>439165</v>
+      </c>
+      <c r="B309" t="n">
+        <v>448460</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>袁天綱;袁天綱</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>92366</v>
+      </c>
+      <c r="B310" t="n">
+        <v>186224</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>盧肇;盧肇</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>131775</v>
+      </c>
+      <c r="B311" t="n">
+        <v>364505</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>楊廷麟;楊廷麟</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>12255</v>
+      </c>
+      <c r="B312" t="n">
+        <v>146954</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>蕭統;蕭統</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>12255</v>
+      </c>
+      <c r="B313" t="n">
+        <v>339548</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>蕭統;蕭統</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>82003</v>
+      </c>
+      <c r="B314" t="n">
+        <v>372414</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>陳鍾麟;陳鍾麟</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>81286</v>
+      </c>
+      <c r="B315" t="n">
+        <v>125624</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>陸增祥;陸增祥</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>132061</v>
+      </c>
+      <c r="B316" t="n">
+        <v>219333</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>鄒觀光;鄒觀光</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>62505</v>
+      </c>
+      <c r="B317" t="n">
+        <v>264037</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>王恕;王恕</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>68414</v>
+      </c>
+      <c r="B318" t="n">
+        <v>328182</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>黃正色;黃正色</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>33502</v>
+      </c>
+      <c r="B319" t="n">
+        <v>33510</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>李習仁;李習仁</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>30328</v>
+      </c>
+      <c r="B320" t="n">
+        <v>327121</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>項元汴;項元汴</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>84043</v>
+      </c>
+      <c r="B321" t="n">
+        <v>344880</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>項名達;項名達</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>67331</v>
+      </c>
+      <c r="B322" t="n">
+        <v>262791</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>黎淳;黎淳</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>65690</v>
+      </c>
+      <c r="B323" t="n">
+        <v>338899</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>齊召南;齊召南</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>74707</v>
+      </c>
+      <c r="B324" t="n">
+        <v>361014</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>莊培因;莊培因</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>34573</v>
+      </c>
+      <c r="B325" t="n">
+        <v>271557</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>賀欽;賀欽</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>132448</v>
+      </c>
+      <c r="B326" t="n">
+        <v>373983</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>歐陽東鳳;歐陽東鳳</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>132448</v>
+      </c>
+      <c r="B327" t="n">
+        <v>470613</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>歐陽東鳳;歐陽東鳳</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>125658</v>
+      </c>
+      <c r="B328" t="n">
+        <v>338400</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>賀濤;賀濤</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>81516</v>
+      </c>
+      <c r="B329" t="n">
+        <v>371045</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>陳三立;陳三立</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>88036</v>
+      </c>
+      <c r="B330" t="n">
+        <v>362749</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>黃濬;黃濬</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>89501</v>
+      </c>
+      <c r="B331" t="n">
+        <v>125625</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>董祐誠;董祐誠</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>126680</v>
+      </c>
+      <c r="B332" t="n">
+        <v>329590</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>王問;王問</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>91195</v>
+      </c>
+      <c r="B333" t="n">
+        <v>125632</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>譚敬昭;譚敬昭</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>90438</v>
+      </c>
+      <c r="B334" t="n">
+        <v>131687</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>溫璜;溫璜</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>90438</v>
+      </c>
+      <c r="B335" t="n">
+        <v>356792</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>溫璜;溫璜</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>56580</v>
+      </c>
+      <c r="B336" t="n">
+        <v>439074</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>茅元儀;茅元儀</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>29571</v>
+      </c>
+      <c r="B337" t="n">
+        <v>261806</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>李承箕;李承箕</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>209075</v>
+      </c>
+      <c r="B338" t="n">
+        <v>340474</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>謝廷讚;謝廷讚</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>131430</v>
+      </c>
+      <c r="B339" t="n">
+        <v>363048</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>黃景昉;黃景昉</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>29580</v>
+      </c>
+      <c r="B340" t="n">
+        <v>372146</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>陳邦瞻;陳邦瞻</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>129368</v>
+      </c>
+      <c r="B341" t="n">
+        <v>339247</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>高出;高出</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>372956</v>
+      </c>
+      <c r="B342" t="n">
+        <v>438263</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>周永春;周永春</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>66274</v>
+      </c>
+      <c r="B343" t="n">
+        <v>107551</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>章溢;章溢</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>117786</v>
+      </c>
+      <c r="B344" t="n">
+        <v>131527</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>華悰韡;華宗鞾</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>83179</v>
+      </c>
+      <c r="B345" t="n">
+        <v>373405</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>周鍾;周鍾</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>79982</v>
+      </c>
+      <c r="B346" t="n">
+        <v>130425</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>張采;張采</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>133643</v>
+      </c>
+      <c r="B347" t="n">
+        <v>355469</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>顧秉謙;顧秉謙</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>122508</v>
+      </c>
+      <c r="B348" t="n">
+        <v>352783</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>倪仁禎;倪仁禎</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>126402</v>
+      </c>
+      <c r="B349" t="n">
+        <v>339108</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>方岳貢;方岳貢</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>30861</v>
+      </c>
+      <c r="B350" t="n">
+        <v>32479</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>杜淹;杜淹</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>207853</v>
+      </c>
+      <c r="B351" t="n">
+        <v>332421</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>楊瑛;楊瑛</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>66632</v>
+      </c>
+      <c r="B352" t="n">
+        <v>131399</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>黃彥清;黃彥清</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>245566</v>
+      </c>
+      <c r="B353" t="n">
+        <v>355587</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>顧巽;顧巽</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>122198</v>
+      </c>
+      <c r="B354" t="n">
+        <v>133380</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>鍾惺;鍾惺</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>30190</v>
+      </c>
+      <c r="B355" t="n">
+        <v>123565</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>屈大均;屈大均</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>20536</v>
+      </c>
+      <c r="B356" t="n">
+        <v>381528</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>陸希聲;陸希聲</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>36888</v>
+      </c>
+      <c r="B357" t="n">
+        <v>46790</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>范氏(張琬妻);范氏(張琬妻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>5009</v>
+      </c>
+      <c r="B358" t="n">
+        <v>49116</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>陳氏(程琳妻);陳氏(程琳妻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>5046</v>
+      </c>
+      <c r="B359" t="n">
+        <v>48888</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>鄧氏(賀允中妻;鄧氏(賀允中妻</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>131188</v>
+      </c>
+      <c r="B360" t="n">
+        <v>206140</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>游樸;游樸</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>131188</v>
+      </c>
+      <c r="B361" t="n">
+        <v>509088</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>游樸;游朴</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>204171</v>
+      </c>
+      <c r="B362" t="n">
+        <v>315141</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>趙祖鵬;趙祖鵬</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>68236</v>
+      </c>
+      <c r="B363" t="n">
+        <v>324953</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>霍韜;霍韜</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>33171</v>
+      </c>
+      <c r="B364" t="n">
+        <v>128488</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>祁承㸁;祁承㸁</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>33171</v>
+      </c>
+      <c r="B365" t="n">
+        <v>357011</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>祁承㸁;祁承㸁</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>34501</v>
+      </c>
+      <c r="B366" t="n">
+        <v>250264</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>劉球;劉球</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>90595</v>
+      </c>
+      <c r="B367" t="n">
+        <v>340634</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>謝泰宗;謝泰宗</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>233848</v>
+      </c>
+      <c r="B368" t="n">
+        <v>364367</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>賀燦然;賀燦然</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>132043</v>
+      </c>
+      <c r="B369" t="n">
+        <v>319449</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>鄒守益;鄒守益</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>33187</v>
+      </c>
+      <c r="B370" t="n">
+        <v>133119</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>錢琦;錢琦</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>33187</v>
+      </c>
+      <c r="B371" t="n">
+        <v>298505</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>錢琦;錢琦</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>130777</v>
+      </c>
+      <c r="B372" t="n">
+        <v>371035</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>陳一元;陳一元</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>204233</v>
+      </c>
+      <c r="B373" t="n">
+        <v>212364</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>馬自強;馬自強</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>216128</v>
+      </c>
+      <c r="B374" t="n">
+        <v>230672</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>黃洪憲;黃洪憲</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>133673</v>
+      </c>
+      <c r="B375" t="n">
+        <v>355531</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>顧夢圭;顧夢圭</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>203738</v>
+      </c>
+      <c r="B376" t="n">
+        <v>336237</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>李一元;李一元</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>131954</v>
+      </c>
+      <c r="B377" t="n">
+        <v>363524</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>葉良佩;葉良佩</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>132606</v>
+      </c>
+      <c r="B378" t="n">
+        <v>229269</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>蔡獻臣;蔡獻臣</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>132606</v>
+      </c>
+      <c r="B379" t="n">
+        <v>363271</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>蔡獻臣;蔡獻臣</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>89912</v>
+      </c>
+      <c r="B380" t="n">
+        <v>352491</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>程崟;程崟</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>266609</v>
+      </c>
+      <c r="B381" t="n">
+        <v>352620</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>程昌;程昌</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>90896</v>
+      </c>
+      <c r="B382" t="n">
+        <v>354419</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>竇垿;竇垿</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>256030</v>
+      </c>
+      <c r="B383" t="n">
+        <v>324163</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>王琦;王琦</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>128667</v>
+      </c>
+      <c r="B384" t="n">
+        <v>359812</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>來宗道;來宗道</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>202120</v>
+      </c>
+      <c r="B385" t="n">
+        <v>214655</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>司馬相;司馬相</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>202120</v>
+      </c>
+      <c r="B386" t="n">
+        <v>316531</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>司馬相;司馬相</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>67063</v>
+      </c>
+      <c r="B387" t="n">
+        <v>344351</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>夏時;夏時</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>129799</v>
+      </c>
+      <c r="B388" t="n">
+        <v>212349</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>孫鏊;孫鏊</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>129799</v>
+      </c>
+      <c r="B389" t="n">
+        <v>315634</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>孫鏊;孫鏊</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>129799</v>
+      </c>
+      <c r="B390" t="n">
+        <v>319049</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>孫鏊;孫鏊</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>129799</v>
+      </c>
+      <c r="B391" t="n">
+        <v>336084</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>孫鏊;孫鏊</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>125530</v>
+      </c>
+      <c r="B392" t="n">
+        <v>334797</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>張岳;張岳</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>79952</v>
+      </c>
+      <c r="B393" t="n">
+        <v>283233</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>張遠;張遠</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>127329</v>
+      </c>
+      <c r="B394" t="n">
+        <v>328387</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>朱袞;朱袞</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>77517</v>
+      </c>
+      <c r="B395" t="n">
+        <v>358161</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>李安世;李安世</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>71552</v>
+      </c>
+      <c r="B396" t="n">
+        <v>342295</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>王先吉;王先吉</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>28798</v>
+      </c>
+      <c r="B397" t="n">
+        <v>254720</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>王冕;王冕</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>71277</v>
+      </c>
+      <c r="B398" t="n">
+        <v>100968</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>王霖;王霖</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>33171</v>
+      </c>
+      <c r="B399" t="n">
+        <v>128488</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>祁承㸁;祁承㸁</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>33171</v>
+      </c>
+      <c r="B400" t="n">
+        <v>357011</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>祁承㸁;祁承㸁</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>203515</v>
+      </c>
+      <c r="B401" t="n">
+        <v>323988</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>胡安;胡安</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>198877</v>
+      </c>
+      <c r="B402" t="n">
+        <v>243203</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>胡恭;胡恭</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>43049</v>
+      </c>
+      <c r="B403" t="n">
+        <v>104887</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>胡渭;胡渭</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>201903</v>
+      </c>
+      <c r="B404" t="n">
+        <v>306973</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>葛木;葛木</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>90597</v>
+      </c>
+      <c r="B405" t="n">
+        <v>442381</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>謝起龍;謝起龍</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>132403</v>
+      </c>
+      <c r="B406" t="n">
+        <v>215583</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>鄭舜臣;鄭舜臣</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>113061</v>
+      </c>
+      <c r="B407" t="n">
+        <v>126368</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>釋大同;釋大同</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>81374</v>
+      </c>
+      <c r="B408" t="n">
+        <v>130946</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>陳塏;陳塏</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>81374</v>
+      </c>
+      <c r="B409" t="n">
+        <v>371908</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>陳塏;陳塏</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>203551</v>
+      </c>
+      <c r="B410" t="n">
+        <v>296253</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>陳絳;陳絳</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>203551</v>
+      </c>
+      <c r="B411" t="n">
+        <v>314961</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>陳絳;陳絳</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>204139</v>
+      </c>
+      <c r="B412" t="n">
+        <v>296255</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>陳綰;陳綰</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>81456</v>
+      </c>
+      <c r="B413" t="n">
+        <v>108070</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>陳謨;陳謨</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>81456</v>
+      </c>
+      <c r="B414" t="n">
+        <v>199468</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>陳謨;陳謨</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>81456</v>
+      </c>
+      <c r="B415" t="n">
+        <v>371012</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>陳謨;陳謨</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>309528</v>
+      </c>
+      <c r="B416" t="n">
+        <v>323310</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>陶廷奎;陶廷奎</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>133718</v>
+      </c>
+      <c r="B417" t="n">
+        <v>340398</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>龔輝;龔輝</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>128931</v>
+      </c>
+      <c r="B418" t="n">
+        <v>220217</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>周應賓;周應賓</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>135127</v>
+      </c>
+      <c r="B419" t="n">
+        <v>339715</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>完顏允恭;完顏允恭</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>87934</v>
+      </c>
+      <c r="B420" t="n">
+        <v>360944</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>堵胤錫;堵胤錫</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>128931</v>
+      </c>
+      <c r="B421" t="n">
+        <v>220217</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>周應賓;周應賓</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>127627</v>
+      </c>
+      <c r="B422" t="n">
+        <v>232068</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>沈節甫;沈節甫</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>127627</v>
+      </c>
+      <c r="B423" t="n">
+        <v>224528</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>沈節甫;沈節甫</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>130782</v>
+      </c>
+      <c r="B424" t="n">
+        <v>371097</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>陳于廷;陳于廷</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>235440</v>
+      </c>
+      <c r="B425" t="n">
+        <v>355553</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>顧起元;顧起元</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>131573</v>
+      </c>
+      <c r="B426" t="n">
+        <v>237105</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>焦宏;焦宏</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>131573</v>
+      </c>
+      <c r="B427" t="n">
+        <v>240759</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>焦宏;焦宏</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>28093</v>
+      </c>
+      <c r="B428" t="n">
+        <v>511342</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>方孝孺;方孝儒</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>68092</v>
+      </c>
+      <c r="B429" t="n">
+        <v>217391</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>楊廷和;楊廷和</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>68092</v>
+      </c>
+      <c r="B430" t="n">
+        <v>275716</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>楊廷和;楊廷和</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>35222</v>
+      </c>
+      <c r="B431" t="n">
+        <v>229489</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>袁宏道;袁宏道</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>128587</v>
+      </c>
+      <c r="B432" t="n">
+        <v>313667</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>林兆恩;林兆恩</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>130245</v>
+      </c>
+      <c r="B433" t="n">
+        <v>366036</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>梅之煥;梅之煥</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>127561</v>
+      </c>
+      <c r="B434" t="n">
+        <v>272633</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>沈灼;沈爚</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>71684</v>
+      </c>
+      <c r="B435" t="n">
+        <v>342982</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>王希旦;王希旦</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>135086</v>
+      </c>
+      <c r="B436" t="n">
+        <v>289880</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>陳昌積;陳昌積</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>128374</v>
+      </c>
+      <c r="B437" t="n">
+        <v>337057</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>余懋孳;余懋孳</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>128374</v>
+      </c>
+      <c r="B438" t="n">
+        <v>374872</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>余懋孳;余懋孳</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>87907</v>
+      </c>
+      <c r="B439" t="n">
+        <v>373485</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>陶崇道;陶崇道</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>86686</v>
+      </c>
+      <c r="B440" t="n">
+        <v>353951</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>徐芳;徐芳</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>219197</v>
+      </c>
+      <c r="B441" t="n">
+        <v>364232</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>林民止;林民止</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>205702</v>
+      </c>
+      <c r="B442" t="n">
+        <v>221210</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>黃猷吉;黃猷吉</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>205702</v>
+      </c>
+      <c r="B443" t="n">
+        <v>363136</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>黃猷吉;黃猷吉</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>741</v>
+      </c>
+      <c r="B444" t="n">
+        <v>537887</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>熊彥詩;熊彥詩</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>94651</v>
+      </c>
+      <c r="B445" t="n">
+        <v>447460</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>梁肅;梁肅</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>94651</v>
+      </c>
+      <c r="B446" t="n">
+        <v>165697</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>梁肅;梁肅</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>94651</v>
+      </c>
+      <c r="B447" t="n">
+        <v>190585</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>梁肅;梁肅</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>28603</v>
+      </c>
+      <c r="B448" t="n">
+        <v>419715</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>胡衹遹;胡祗遹</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>106657</v>
+      </c>
+      <c r="B449" t="n">
+        <v>386141</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>張復;張復</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>33424</v>
+      </c>
+      <c r="B450" t="n">
+        <v>112184</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>衛培;衛培</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>34528</v>
+      </c>
+      <c r="B451" t="n">
+        <v>128234</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>吳溥;吳溥</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>43829</v>
+      </c>
+      <c r="B452" t="n">
+        <v>151114</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>釋道一;道一</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>434420</v>
+      </c>
+      <c r="B453" t="n">
+        <v>511824</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>駱仲明;賈仲明</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>290050</v>
+      </c>
+      <c r="B454" t="n">
+        <v>310258</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>周如登;周如登</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>131205</v>
+      </c>
+      <c r="B455" t="n">
+        <v>356869</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>湯賓尹;湯賓尹</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>34700</v>
+      </c>
+      <c r="B456" t="n">
+        <v>304155</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>王慎中;王慎中</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>34700</v>
+      </c>
+      <c r="B457" t="n">
+        <v>343916</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>王慎中;王慎中</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>134679</v>
+      </c>
+      <c r="B458" t="n">
+        <v>504918</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>沈約;沈約</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>128843</v>
+      </c>
+      <c r="B459" t="n">
+        <v>373446</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>周炳謨;周炳謨</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>126629</v>
+      </c>
+      <c r="B460" t="n">
+        <v>342532</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>王家植;王家植</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>122220</v>
+      </c>
+      <c r="B461" t="n">
+        <v>126629</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>王家植;潘之恆</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>126629</v>
+      </c>
+      <c r="B462" t="n">
+        <v>132309</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>王家植;潘之恆</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>128843</v>
+      </c>
+      <c r="B463" t="n">
+        <v>373446</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>周炳謨;周炳謨</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>132357</v>
+      </c>
+      <c r="B464" t="n">
+        <v>375475</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>鄭以偉;鄭以偉</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>59966</v>
+      </c>
+      <c r="B465" t="n">
+        <v>357548</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>李天經;李天經</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>24353</v>
+      </c>
+      <c r="B466" t="n">
+        <v>511647</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>葛長庚;白玉蟾</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>59966</v>
+      </c>
+      <c r="B467" t="n">
+        <v>357548</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>李天經;李天經</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>22469</v>
+      </c>
+      <c r="B468" t="n">
+        <v>93128</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>李翱;李翺</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>22469</v>
+      </c>
+      <c r="B469" t="n">
+        <v>189536</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>李翱;李翺</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>22469</v>
+      </c>
+      <c r="B470" t="n">
+        <v>189795</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>李翱;李翺</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>34625</v>
+      </c>
+      <c r="B471" t="n">
+        <v>263976</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>李正;李正</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>66032</v>
+      </c>
+      <c r="B472" t="n">
+        <v>510911</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>朱彜尊;朱彛尊</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>177131</v>
+      </c>
+      <c r="B473" t="n">
+        <v>446733</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>崔龜從;崔龜從</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>126312</v>
+      </c>
+      <c r="B474" t="n">
+        <v>344162</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>丁奉;丁奉</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>55365</v>
+      </c>
+      <c r="B475" t="n">
+        <v>566367</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>龍錢潔;錢潔</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>55346</v>
+      </c>
+      <c r="B476" t="n">
+        <v>566408</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>湯淑英;湯淑英</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>122816</v>
+      </c>
+      <c r="B477" t="n">
+        <v>566506</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>楊徹;楊徹</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>135275</v>
+      </c>
+      <c r="B478" t="n">
+        <v>374346</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>俞琬綸;俞琬綸</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>129208</v>
+      </c>
+      <c r="B479" t="n">
+        <v>439204</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>俞允文;俞允文</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>130605</v>
+      </c>
+      <c r="B480" t="n">
+        <v>578877</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>張鳳翼;張鳳翼</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>565471</v>
+      </c>
+      <c r="B481" t="n">
+        <v>566614</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>朱柔英;朱柔英</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>68166</v>
+      </c>
+      <c r="B482" t="n">
+        <v>130832</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>陳束;陳束</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>68166</v>
+      </c>
+      <c r="B483" t="n">
+        <v>123161</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>陳束;董氏(陳束妻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>68166</v>
+      </c>
+      <c r="B484" t="n">
+        <v>287346</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>陳束;董氏(陳束妻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>127729</v>
+      </c>
+      <c r="B485" t="n">
+        <v>560897</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>杜瓊;杜瓊</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>127729</v>
+      </c>
+      <c r="B486" t="n">
+        <v>259487</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>杜瓊;杜瓊</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>245058</v>
+      </c>
+      <c r="B487" t="n">
+        <v>525515</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>吳融;吳孟融</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>270014</v>
+      </c>
+      <c r="B488" t="n">
+        <v>328384</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>朱顥;朱顥</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>34581</v>
+      </c>
+      <c r="B489" t="n">
+        <v>247601</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>王琬（Wang Wan(5)）-;王朝用（Wang Chaoyong）-</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>30681</v>
+      </c>
+      <c r="B490" t="n">
+        <v>351259</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>皇甫汸;皇甫方</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>30676</v>
+      </c>
+      <c r="B491" t="n">
+        <v>290228</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>皇甫錄;皇甫錄</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>129208</v>
+      </c>
+      <c r="B492" t="n">
+        <v>439204</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>俞允文;俞允文</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>20555</v>
+      </c>
+      <c r="B493" t="n">
+        <v>511059</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>危稹;危稹</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>35295</v>
+      </c>
+      <c r="B494" t="n">
+        <v>510977</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>俞桂;俞桂</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>22701</v>
+      </c>
+      <c r="B495" t="n">
+        <v>511755</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>葉紹翁;葉紹翁</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>48073</v>
+      </c>
+      <c r="B496" t="n">
+        <v>511975</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>陳鑒之;陳鑒之</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>43098</v>
+      </c>
+      <c r="B497" t="n">
+        <v>511352</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>施樞;施樞</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>27798</v>
+      </c>
+      <c r="B498" t="n">
+        <v>511803</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>許棐;許棐</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>40057</v>
+      </c>
+      <c r="B499" t="n">
+        <v>511386</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>朱繼芳;朱繼芳</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>30225</v>
+      </c>
+      <c r="B500" t="n">
+        <v>512084</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>黃文雷;黃文雷</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>42614</v>
+      </c>
+      <c r="B501" t="n">
+        <v>511113</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>周文璞;周文璞</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>133092</v>
+      </c>
+      <c r="B502" t="n">
+        <v>375090</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>錢仁夫;錢仁夫</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>126312</v>
+      </c>
+      <c r="B503" t="n">
+        <v>344162</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>丁奉;丁奉</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>133065</v>
+      </c>
+      <c r="B504" t="n">
+        <v>348926</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>盧襄;盧襄</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>35261</v>
+      </c>
+      <c r="B505" t="n">
+        <v>301102</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>袁袠;袁袠</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>439124</v>
+      </c>
+      <c r="B506" t="n">
+        <v>559755</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>袁表;袁表</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>35256</v>
+      </c>
+      <c r="B507" t="n">
+        <v>301099</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>袁表;袁表</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>218946</v>
+      </c>
+      <c r="B508" t="n">
+        <v>301101</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>袁褒;袁褒</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>126804</v>
+      </c>
+      <c r="B509" t="n">
+        <v>343301</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>王穀祥;王穀祥</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>128536</v>
+      </c>
+      <c r="B510" t="n">
+        <v>226311</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>邵圭潔;邵圭潔</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>35262</v>
+      </c>
+      <c r="B511" t="n">
+        <v>218953</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>袁尊尼;袁尊尼</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>130605</v>
+      </c>
+      <c r="B512" t="n">
+        <v>578877</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>張鳳翼;張鳳翼</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>71654</v>
+      </c>
+      <c r="B513" t="n">
+        <v>235156</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>王志長;王志長</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>135275</v>
+      </c>
+      <c r="B514" t="n">
+        <v>374346</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>俞琬綸;俞琬綸</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>35040</v>
+      </c>
+      <c r="B515" t="n">
+        <v>118840</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>王穉登;王稚登</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>35040</v>
+      </c>
+      <c r="B516" t="n">
+        <v>577136</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>王穉登;王穉登</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>66884</v>
+      </c>
+      <c r="B517" t="n">
+        <v>240883</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>吳訥;吳訥</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>34581</v>
+      </c>
+      <c r="B518" t="n">
+        <v>247601</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>王朝用;王琬</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>128402</v>
+      </c>
+      <c r="B519" t="n">
+        <v>303087</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>何良俊;何良俊</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>128402</v>
+      </c>
+      <c r="B520" t="n">
+        <v>303087</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>何良俊;何良俊</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>126312</v>
+      </c>
+      <c r="B521" t="n">
+        <v>344162</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>丁奉;丁奉</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>204294</v>
+      </c>
+      <c r="B522" t="n">
+        <v>217187</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>秦可大;秦可大</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>92525</v>
+      </c>
+      <c r="B523" t="n">
+        <v>446935</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>朱長文;朱長文</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>326164</v>
+      </c>
+      <c r="B524" t="n">
+        <v>333658</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>王夢祥;王夢祥</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>130769</v>
+      </c>
+      <c r="B525" t="n">
+        <v>370687</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>陸應龍;陸應龍</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>65871</v>
+      </c>
+      <c r="B526" t="n">
+        <v>126213</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>金人瑞;金人瑞</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>124003</v>
+      </c>
+      <c r="B527" t="n">
+        <v>326167</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>王鼎爵;王鼎爵</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
         <v>32024</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B528" t="n">
+        <v>93470</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>張彥遠;張彥遠</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>32024</v>
+      </c>
+      <c r="B529" t="n">
         <v>380725</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C529" t="inlineStr">
         <is>
           <t>張彥遠;張彥遠</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>41093</v>
+      </c>
+      <c r="B530" t="n">
+        <v>468593</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>李重進;李重進</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>95092</v>
+      </c>
+      <c r="B531" t="n">
+        <v>155852</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>魏玄同;魏玄同</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>135353</v>
+      </c>
+      <c r="B532" t="n">
+        <v>339525</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>劉備;劉備</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>204478</v>
+      </c>
+      <c r="B533" t="n">
+        <v>216734</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>史朝寀;史朝寀</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>204478</v>
+      </c>
+      <c r="B534" t="n">
+        <v>308526</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>史朝寀;史朝寀</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>204478</v>
+      </c>
+      <c r="B535" t="n">
+        <v>316597</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>史朝寀;史朝寀</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>204478</v>
+      </c>
+      <c r="B536" t="n">
+        <v>318053</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>史朝寀;史朝寀</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>204478</v>
+      </c>
+      <c r="B537" t="n">
+        <v>336458</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>史朝寀;史朝寀</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>31736</v>
+      </c>
+      <c r="B538" t="n">
+        <v>155010</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>盧杞;盧杞</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>32478</v>
+      </c>
+      <c r="B539" t="n">
+        <v>173287</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>杜景秀;杜景秀</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>32477</v>
+      </c>
+      <c r="B540" t="n">
+        <v>173277</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>杜顒;杜顒</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>32477</v>
+      </c>
+      <c r="B541" t="n">
+        <v>462805</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>杜顒;杜顒</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>92151</v>
+      </c>
+      <c r="B542" t="n">
+        <v>179850</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>韋元甫;韋元甫</t>
         </is>
       </c>
     </row>
